--- a/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1183,6 +1183,16 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>RewardKind</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>UpgradeDefinitionId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1225,6 +1235,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1267,6 +1287,16 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RewardKind</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>UpgradeDefinitionId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1297,6 +1327,16 @@
       <c r="H4">
         <v>0</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1326,6 +1366,120 @@
       </c>
       <c r="H5">
         <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>升级切配台</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>升级烤箱</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1482,6 +1482,86 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>新增台面</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>新增切配台</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/RenovationConfig.xlsx
@@ -939,636 +939,1039 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quantity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InstallX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InstallY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Orientation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RewardKind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UpgradeDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" t="str">
-        <x:v>UnlockDishIds</x:v>
-      </x:c>
-      <x:c r="L1" t="str">
-        <x:v>UnlockStationIds</x:v>
-      </x:c>
-      <x:c r="M1" t="str">
-        <x:v>ExpansionWidth</x:v>
-      </x:c>
-      <x:c r="N1" t="str">
-        <x:v>ExpansionHeight</x:v>
-      </x:c>
-      <x:c r="O1" t="str">
-        <x:v>TableDefinitionId</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>RenovationRewardKind</x:v>
-      </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>(list#sep=,),int</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>(list#sep=,),int</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="O2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quantity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InstallX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InstallY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Orientation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RewardKind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UpgradeDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>解锁菜品定义</x:v>
-      </x:c>
-      <x:c r="L3" t="str">
-        <x:v>解锁设备定义</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>扩建后宽度</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
-        <x:v>扩建后高度</x:v>
-      </x:c>
-      <x:c r="O3" t="str">
-        <x:v>扩建单客桌定义</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增台面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G4">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H4">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" t="str"/>
-      <x:c r="L4" t="str"/>
-      <x:c r="M4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增切配台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G5">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" t="str"/>
-      <x:c r="L5" t="str"/>
-      <x:c r="M5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">升级切配台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" t="str"/>
-      <x:c r="L6" t="str"/>
-      <x:c r="M6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">升级烤箱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K7" t="str"/>
-      <x:c r="L7" t="str"/>
-      <x:c r="M7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增台面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G8">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K8" t="str"/>
-      <x:c r="L8" t="str"/>
-      <x:c r="M8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B9">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增切配台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K9" t="str"/>
-      <x:c r="L9" t="str"/>
-      <x:c r="M9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str"/>
-      <x:c r="B10" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>解锁现榨菜单</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L10" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str"/>
-      <x:c r="B11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>扩建单客桌</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" t="str"/>
-      <x:c r="L11" t="str"/>
-      <x:c r="M11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="N11" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="O11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationDefinitionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InstallX</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InstallY</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orientation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RewardKind</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UpgradeDefinitionId</t>
+        </is>
+      </c>
+      <c r="K1" t="str">
+        <v>UnlockDishIds</v>
+      </c>
+      <c r="L1" t="str">
+        <v>UnlockStationIds</v>
+      </c>
+      <c r="M1" t="str">
+        <v>ExpansionWidth</v>
+      </c>
+      <c r="N1" t="str">
+        <v>ExpansionHeight</v>
+      </c>
+      <c r="O1" t="str">
+        <v>TableDefinitionId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>GridOrientation</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RenovationRewardKind</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="K2" t="str">
+        <v>(list#sep=,),int</v>
+      </c>
+      <c r="L2" t="str">
+        <v>(list#sep=,),int</v>
+      </c>
+      <c r="M2" t="str">
+        <v>int</v>
+      </c>
+      <c r="N2" t="str">
+        <v>int</v>
+      </c>
+      <c r="O2" t="str">
+        <v>int</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationDefinitionId</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InstallX</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InstallY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orientation</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RewardKind</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UpgradeDefinitionId</t>
+        </is>
+      </c>
+      <c r="K3" t="str">
+        <v>解锁菜品定义</v>
+      </c>
+      <c r="L3" t="str">
+        <v>解锁设备定义</v>
+      </c>
+      <c r="M3" t="str">
+        <v>扩建后宽度</v>
+      </c>
+      <c r="N3" t="str">
+        <v>扩建后高度</v>
+      </c>
+      <c r="O3" t="str">
+        <v>扩建单客桌定义</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新增台面</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>13</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>InstallStation</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="K4" t="str"/>
+      <c r="L4" t="str"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新增切配台</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>InstallStation</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="K5" t="str"/>
+      <c r="L5" t="str"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">升级切配台</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="K6" t="str"/>
+      <c r="L6" t="str"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">升级烤箱</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="K7" t="str"/>
+      <c r="L7" t="str"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新增台面</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>InstallStation</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="K8" t="str"/>
+      <c r="L8" t="str"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新增切配台</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>InstallStation</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="K9" t="str"/>
+      <c r="L9" t="str"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str"/>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="str">
+        <v>解锁现榨菜单</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UnlockDefinitions</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <v>3</v>
+      </c>
+      <c r="L10" t="str">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str"/>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="str">
+        <v>扩建单客桌</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ExpandSpace</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str"/>
+      <c r="L11" t="str"/>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str"/>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高效灶台</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str"/>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>高效榨汁机</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str"/>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>高效煎台</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str"/>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>高效搅拌机</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str"/>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>高效磨豆机</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J16">
+        <v>7</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str"/>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高效咖啡机</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J17">
+        <v>8</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str"/>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高效蒸汽机</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Unrotated</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UpgradeStation</t>
+        </is>
+      </c>
+      <c r="J18">
+        <v>9</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>